--- a/scouting_merged.xlsx
+++ b/scouting_merged.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:Q7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -654,70 +654,350 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Collin</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>Sybau</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03T18:42:57.859Z</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr">
+        <is>
+          <t>scouting_2026-04-03 (1).csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B3" s="3" t="n">
+      <c r="B4" s="2" t="n">
         <v>5460</v>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Red</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Joe</t>
         </is>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E4" s="2" t="n">
         <v>47</v>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v/>
-      </c>
-      <c r="H3" s="3" t="n">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v/>
+      </c>
+      <c r="H4" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="I3" s="3" t="n">
+      <c r="I4" s="2" t="n">
         <v>95</v>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="K3" s="3" t="n">
-        <v/>
-      </c>
-      <c r="L3" s="3" t="n">
+      <c r="K4" s="2" t="n">
+        <v/>
+      </c>
+      <c r="L4" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="M3" s="3" t="n">
+      <c r="M4" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>drum shooter</t>
         </is>
       </c>
-      <c r="P3" s="3" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>2026-04-01T19:11:43.244Z</t>
         </is>
       </c>
-      <c r="Q3" s="3" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>scouting_2026-04-01.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>8767</v>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Liz</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>Trench</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v/>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>Got penalty</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03T18:43:45.294Z</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t>scouting_2026-04-03 (4).csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>5460</v>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Peyton</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v/>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Trench</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v/>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>Hfhfudhhdhdhdj</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-03T18:38:57.890Z</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>scouting_2026-04-03 (3).csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Joe</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v/>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>drum shooter</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03T18:42:35.110Z</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>scouting_2026-04-03 (2).csv</t>
         </is>
       </c>
     </row>
@@ -732,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -825,10 +1105,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>5460</v>
+        <v>27</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>5</v>
+        <v>63</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -847,10 +1127,10 @@
         <v/>
       </c>
       <c r="G2" s="2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
@@ -861,7 +1141,7 @@
         <v/>
       </c>
       <c r="K2" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>5</v>
@@ -879,55 +1159,275 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>Sybau</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>5460</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v/>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>drum shooter</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>5460</v>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v/>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Trench</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v/>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Hfhfudhhdhdhdj</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
         <v>8767</v>
       </c>
-      <c r="B3" s="3" t="n">
+      <c r="B6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Red</t>
         </is>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D6" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v/>
-      </c>
-      <c r="G3" s="3" t="n">
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G6" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="H6" s="2" t="n">
         <v>85</v>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>Trench</t>
         </is>
       </c>
-      <c r="J3" s="3" t="n">
-        <v/>
-      </c>
-      <c r="K3" s="3" t="n">
+      <c r="J6" s="2" t="n">
+        <v/>
+      </c>
+      <c r="K6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="L3" s="3" t="n">
+      <c r="L6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>dual shooter</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>8767</v>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v/>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>Trench</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v/>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Got penalty</t>
         </is>
       </c>
     </row>
@@ -942,7 +1442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -999,7 +1499,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>5460</v>
+        <v>27</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>1</v>
@@ -1008,16 +1508,16 @@
         <v>47</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>5</v>
@@ -1025,19 +1525,19 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>8767</v>
+        <v>5460</v>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>0</v>
@@ -1046,7 +1546,59 @@
         <v>4</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>5</v>
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>8767</v>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
